--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E19EC5A4-9685-48E3-A3F8-C6744EC6F0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9DA179C-5B83-4635-89E4-1C2031611E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -877,16 +877,142 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_003</t>
@@ -895,205 +1021,91 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1024536785-380,e_w26593929-380,e_DE159-380,e_w26777313-380,e_w160584794-380,e_w152403632-380,e_w38661452-380,e_DE157-380</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w1280178911-380,e_w31024391-380</t>
+  </si>
+  <si>
+    <t>e_w797009308-380,e_w1128250704-380,e_w883928229-380,e_w951773852-380,e_w32076853-380,e_w955268864-380</t>
+  </si>
+  <si>
     <t>e_w5404079-380,e_w26245195-380,e_w24976300-380</t>
   </si>
   <si>
+    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
+  </si>
+  <si>
+    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
+  </si>
+  <si>
+    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
+  </si>
+  <si>
+    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
+  </si>
+  <si>
+    <t>e_DE118-380,e_DE69-380,e_w33816726-380,e_DE87-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
+  </si>
+  <si>
+    <t>e_w1072574879-380,e_w30622610-380,e_DE20-380,e_w11285720-380,e_w25306938-380,e_w28343121-380,e_w1089911133-380,e_w1102237380-380,e_w30040568-380,e_w275466323</t>
+  </si>
+  <si>
+    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
+  </si>
+  <si>
+    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
+  </si>
+  <si>
+    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
+  </si>
+  <si>
+    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
+  </si>
+  <si>
+    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
+  </si>
+  <si>
+    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
+  </si>
+  <si>
+    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
+  </si>
+  <si>
+    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
+  </si>
+  <si>
+    <t>e_w31131325-380,e_w25306752-380,e_w31131320-380,e_w41389594-380,e_w57727004-380,e_w683227471-380,e_w88945213-380,e_DE240-380,e_w30613895-380,e_w53378027-380</t>
+  </si>
+  <si>
+    <t>e_w947118608-380,e_w941453716-380,e_w30039908-380,e_w1091984573-380,e_DE21-400,e_w943444232-380</t>
+  </si>
+  <si>
     <t>e_w26245195-380,e_w137602559-380,e_w77697810-380,e_w24976300-380,e_DE183-380</t>
   </si>
   <si>
-    <t>e_DE118-380,e_DE69-380,e_w33816726-380,e_DE87-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
-  </si>
-  <si>
-    <t>e_w1072574879-380,e_w30622610-380,e_DE20-380,e_w11285720-380,e_w25306938-380,e_w28343121-380,e_w1089911133-380,e_w1102237380-380,e_w30040568-380,e_w275466323</t>
-  </si>
-  <si>
-    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
-  </si>
-  <si>
-    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
-  </si>
-  <si>
-    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
-  </si>
-  <si>
-    <t>e_w31131325-380,e_w25306752-380,e_w31131320-380,e_w41389594-380,e_w57727004-380,e_w683227471-380,e_w88945213-380,e_DE240-380,e_w30613895-380,e_w53378027-380</t>
-  </si>
-  <si>
-    <t>e_w947118608-380,e_w941453716-380,e_w30039908-380,e_w1091984573-380,e_DE21-400,e_w943444232-380</t>
-  </si>
-  <si>
-    <t>e_w1024536785-380,e_w26593929-380,e_DE159-380,e_w26777313-380,e_w160584794-380,e_w152403632-380,e_w38661452-380,e_DE157-380</t>
-  </si>
-  <si>
-    <t>e_DE23-380,e_w1280178911-380,e_w31024391-380</t>
-  </si>
-  <si>
-    <t>e_w797009308-380,e_w1128250704-380,e_w883928229-380,e_w951773852-380,e_w32076853-380,e_w955268864-380</t>
-  </si>
-  <si>
-    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
-  </si>
-  <si>
-    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
-  </si>
-  <si>
-    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
-  </si>
-  <si>
-    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
-  </si>
-  <si>
-    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
-  </si>
-  <si>
-    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
-  </si>
-  <si>
-    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
-  </si>
-  <si>
-    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_004</t>
@@ -1102,6 +1114,90 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_007</t>
   </si>
   <si>
@@ -1132,100 +1228,16 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_DE165-380,e_DE152-380,e_w29713902-380,e_w944960289-380,e_DE138-380,e_w714098678-380,e_w946025110-380,e_DE160-380,e_w109917397-380</t>
   </si>
   <si>
     <t>elc_won_004</t>
@@ -1234,6 +1246,90 @@
     <t>e_DE23-380,e_w797009308-380,e_w1280178911-380,e_w1128250704-380,e_w883928229-380,e_w31024391-380,e_w32076853-380,e_w603661085-380,e_w946969736-380</t>
   </si>
   <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w941453716-380,e_w1091984573-380,e_w943444232-380</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w683227471-380,e_w30613895-380</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w26245195-380,e_w24976300-380</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w24976300-380</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1024536785-380,e_w26593929-380,e_DE118-380,e_DE69-380,e_DE159-380,e_w26777313-380,e_w33816726-380,e_DE87-380,e_w152403632-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w87653464-380,e_w87653464-400,e_w42049947-380,e_w26814283-380,e_w152261133-380,e_DE217-380,e_DE202-380</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w143903369-380,e_w55069713-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w24705761-380,e_w24758329-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w26404600-380,e_w26403575-380,e_w88945213-380,e_w38325076-380,e_w53378027-380,e_w76246159-380</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
+  </si>
+  <si>
     <t>elc_won_007</t>
   </si>
   <si>
@@ -1264,100 +1360,28 @@
     <t>e_w25306752-380,e_w41389594-380</t>
   </si>
   <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w683227471-380,e_w30613895-380</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w941453716-380,e_w1091984573-380,e_w943444232-380</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_DE165-380,e_DE152-380,e_w29713902-380,e_w944960289-380,e_DE138-380,e_w714098678-380,e_w946025110-380,e_DE160-380,e_w109917397-380</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w24976300-380</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w26245195-380,e_w24976300-380</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1024536785-380,e_w26593929-380,e_DE118-380,e_DE69-380,e_DE159-380,e_w26777313-380,e_w33816726-380,e_DE87-380,e_w152403632-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w87653464-380,e_w87653464-400,e_w42049947-380,e_w26814283-380,e_w152261133-380,e_DE217-380,e_DE202-380</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w143903369-380,e_w55069713-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w24705761-380,e_w24758329-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w26404600-380,e_w26403575-380,e_w88945213-380,e_w38325076-380,e_w53378027-380,e_w76246159-380</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_003</t>
@@ -1384,48 +1408,45 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_DE8-380,e_w940919943</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w31024391-380,e_w946969736-380,e_w1134105414-380</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w275466323,e_w234171369-380</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w1280178911-380</t>
+  </si>
+  <si>
     <t>elc_wof_003</t>
   </si>
   <si>
-    <t>e_DE23-380,e_w1280178911-380</t>
-  </si>
-  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -1444,31 +1465,10 @@
     <t>e_DE21-400</t>
   </si>
   <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_DE8-380,e_w940919943</t>
-  </si>
-  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
     <t>e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w31024391-380,e_w946969736-380,e_w1134105414-380</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w275466323,e_w234171369-380</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
   </si>
   <si>
     <t>elc_wof_007</t>
@@ -6618,7 +6618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AD405F-3F4D-401F-82C1-ED2D94AB14BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8748A45D-1393-40CC-A1D0-AC511BEE902A}">
   <dimension ref="B9:BD33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6856,16 +6856,16 @@
         <v>249</v>
       </c>
       <c r="Y11" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="Z11" t="s">
         <v>299</v>
       </c>
       <c r="AA11">
-        <v>0.9966615805732193</v>
+        <v>0.99903141795748496</v>
       </c>
       <c r="AB11">
-        <v>61.204356157646131</v>
+        <v>17.757337446108838</v>
       </c>
       <c r="AD11" t="s">
         <v>248</v>
@@ -6898,10 +6898,10 @@
         <v>367</v>
       </c>
       <c r="AO11">
-        <v>0.9982655473126083</v>
+        <v>0.99821483672858236</v>
       </c>
       <c r="AP11">
-        <v>31.798299268848115</v>
+        <v>32.727993309323963</v>
       </c>
       <c r="AR11" t="s">
         <v>248</v>
@@ -6934,10 +6934,10 @@
         <v>431</v>
       </c>
       <c r="BC11">
-        <v>0.99374840656294539</v>
+        <v>0.99726555940500838</v>
       </c>
       <c r="BD11">
-        <v>114.61254634600208</v>
+        <v>50.131410908180094</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7002,16 +7002,16 @@
         <v>253</v>
       </c>
       <c r="Y12" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="Z12" t="s">
         <v>300</v>
       </c>
       <c r="AA12">
-        <v>0.99783818599396734</v>
+        <v>0.99797139203037322</v>
       </c>
       <c r="AB12">
-        <v>39.633256777265125</v>
+        <v>37.191146109824579</v>
       </c>
       <c r="AD12" t="s">
         <v>248</v>
@@ -7044,10 +7044,10 @@
         <v>369</v>
       </c>
       <c r="AO12">
-        <v>0.9985540071847413</v>
+        <v>0.99851446571821256</v>
       </c>
       <c r="AP12">
-        <v>26.509868279743756</v>
+        <v>27.234795166103936</v>
       </c>
       <c r="AR12" t="s">
         <v>248</v>
@@ -7080,10 +7080,10 @@
         <v>433</v>
       </c>
       <c r="BC12">
-        <v>0.99731983040343442</v>
+        <v>0.99345136660650646</v>
       </c>
       <c r="BD12">
-        <v>49.136442603701539</v>
+        <v>120.05827888071518</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7148,16 +7148,16 @@
         <v>255</v>
       </c>
       <c r="Y13" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="Z13" t="s">
         <v>301</v>
       </c>
       <c r="AA13">
-        <v>0.99902896095987681</v>
+        <v>0.99872758352859059</v>
       </c>
       <c r="AB13">
-        <v>17.802382402257905</v>
+        <v>23.327635309172347</v>
       </c>
       <c r="AD13" t="s">
         <v>248</v>
@@ -7190,10 +7190,10 @@
         <v>371</v>
       </c>
       <c r="AO13">
-        <v>0.99912192348268269</v>
+        <v>0.9982655473126083</v>
       </c>
       <c r="AP13">
-        <v>16.098069484150571</v>
+        <v>31.798299268848115</v>
       </c>
       <c r="AR13" t="s">
         <v>248</v>
@@ -7226,10 +7226,10 @@
         <v>435</v>
       </c>
       <c r="BC13">
-        <v>0.9955056076869333</v>
+        <v>0.99861480954449533</v>
       </c>
       <c r="BD13">
-        <v>82.397192406223127</v>
+        <v>25.395158350918766</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7294,16 +7294,16 @@
         <v>257</v>
       </c>
       <c r="Y14" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="Z14" t="s">
         <v>302</v>
       </c>
       <c r="AA14">
-        <v>0.99815762041917688</v>
+        <v>0.9966615805732193</v>
       </c>
       <c r="AB14">
-        <v>33.776958981757815</v>
+        <v>61.204356157646131</v>
       </c>
       <c r="AD14" t="s">
         <v>248</v>
@@ -7336,10 +7336,10 @@
         <v>373</v>
       </c>
       <c r="AO14">
-        <v>0.99864092836530338</v>
+        <v>0.99753724381235709</v>
       </c>
       <c r="AP14">
-        <v>24.916313302771705</v>
+        <v>45.150530106787691</v>
       </c>
       <c r="AR14" t="s">
         <v>248</v>
@@ -7372,10 +7372,10 @@
         <v>437</v>
       </c>
       <c r="BC14">
-        <v>0.99845350558031343</v>
+        <v>0.98635566783526007</v>
       </c>
       <c r="BD14">
-        <v>28.352397694253892</v>
+        <v>250.14608968689959</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7440,16 +7440,16 @@
         <v>259</v>
       </c>
       <c r="Y15" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Z15" t="s">
         <v>303</v>
       </c>
       <c r="AA15">
-        <v>0.9981906651950686</v>
+        <v>0.9984521235218653</v>
       </c>
       <c r="AB15">
-        <v>33.171138090409563</v>
+        <v>28.377735432469407</v>
       </c>
       <c r="AD15" t="s">
         <v>248</v>
@@ -7482,10 +7482,10 @@
         <v>375</v>
       </c>
       <c r="AO15">
-        <v>0.99840287720275267</v>
+        <v>0.99831023082457615</v>
       </c>
       <c r="AP15">
-        <v>29.280584616200382</v>
+        <v>30.979101549436738</v>
       </c>
       <c r="AR15" t="s">
         <v>248</v>
@@ -7515,13 +7515,13 @@
         <v>438</v>
       </c>
       <c r="BB15" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="BC15">
-        <v>0.99726555940500838</v>
+        <v>0.99374840656294539</v>
       </c>
       <c r="BD15">
-        <v>50.131410908180094</v>
+        <v>114.61254634600208</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7628,10 +7628,10 @@
         <v>377</v>
       </c>
       <c r="AO16">
-        <v>0.99798110605540413</v>
+        <v>0.99810796133130941</v>
       </c>
       <c r="AP16">
-        <v>37.013055650923285</v>
+        <v>34.687375592660409</v>
       </c>
       <c r="AR16" t="s">
         <v>248</v>
@@ -7658,16 +7658,16 @@
         <v>420</v>
       </c>
       <c r="BA16" t="s">
+        <v>439</v>
+      </c>
+      <c r="BB16" t="s">
         <v>440</v>
       </c>
-      <c r="BB16" t="s">
-        <v>441</v>
-      </c>
       <c r="BC16">
-        <v>0.99733561350881073</v>
+        <v>0.99731983040343442</v>
       </c>
       <c r="BD16">
-        <v>48.847085671804372</v>
+        <v>49.136442603701539</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7774,10 +7774,10 @@
         <v>379</v>
       </c>
       <c r="AO17">
-        <v>0.99831023082457615</v>
+        <v>0.99798114961534334</v>
       </c>
       <c r="AP17">
-        <v>30.979101549436738</v>
+        <v>37.012257052039594</v>
       </c>
       <c r="AR17" t="s">
         <v>248</v>
@@ -7804,16 +7804,16 @@
         <v>422</v>
       </c>
       <c r="BA17" t="s">
+        <v>441</v>
+      </c>
+      <c r="BB17" t="s">
         <v>442</v>
       </c>
-      <c r="BB17" t="s">
-        <v>443</v>
-      </c>
       <c r="BC17">
-        <v>0.99345136660650646</v>
+        <v>0.9955056076869333</v>
       </c>
       <c r="BD17">
-        <v>120.05827888071518</v>
+        <v>82.397192406223127</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7878,16 +7878,16 @@
         <v>265</v>
       </c>
       <c r="Y18" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Z18" t="s">
         <v>306</v>
       </c>
       <c r="AA18">
-        <v>0.9982564657516575</v>
+        <v>0.9981906651950686</v>
       </c>
       <c r="AB18">
-        <v>31.964794552945094</v>
+        <v>33.171138090409563</v>
       </c>
       <c r="AD18" t="s">
         <v>248</v>
@@ -7920,10 +7920,10 @@
         <v>381</v>
       </c>
       <c r="AO18">
-        <v>0.99810796133130941</v>
+        <v>0.99838078830661203</v>
       </c>
       <c r="AP18">
-        <v>34.687375592660409</v>
+        <v>29.68554771211182</v>
       </c>
       <c r="AR18" t="s">
         <v>248</v>
@@ -7950,16 +7950,16 @@
         <v>424</v>
       </c>
       <c r="BA18" t="s">
+        <v>443</v>
+      </c>
+      <c r="BB18" t="s">
         <v>444</v>
       </c>
-      <c r="BB18" t="s">
-        <v>445</v>
-      </c>
       <c r="BC18">
-        <v>0.99861480954449533</v>
+        <v>0.99845350558031343</v>
       </c>
       <c r="BD18">
-        <v>25.395158350918766</v>
+        <v>28.352397694253892</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8024,16 +8024,16 @@
         <v>267</v>
       </c>
       <c r="Y19" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="Z19" t="s">
         <v>307</v>
       </c>
       <c r="AA19">
-        <v>0.99854052945036897</v>
+        <v>0.99902896095987681</v>
       </c>
       <c r="AB19">
-        <v>26.756960076568774</v>
+        <v>17.802382402257905</v>
       </c>
       <c r="AD19" t="s">
         <v>248</v>
@@ -8066,10 +8066,10 @@
         <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.99798114961534334</v>
+        <v>0.99852500850690518</v>
       </c>
       <c r="AP19">
-        <v>37.012257052039594</v>
+        <v>27.041510706738034</v>
       </c>
       <c r="AR19" t="s">
         <v>248</v>
@@ -8096,16 +8096,16 @@
         <v>426</v>
       </c>
       <c r="BA19" t="s">
+        <v>445</v>
+      </c>
+      <c r="BB19" t="s">
         <v>446</v>
       </c>
-      <c r="BB19" t="s">
-        <v>431</v>
-      </c>
       <c r="BC19">
-        <v>0.98635566783526007</v>
+        <v>0.99733561350881073</v>
       </c>
       <c r="BD19">
-        <v>250.14608968689959</v>
+        <v>48.847085671804372</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8170,16 +8170,16 @@
         <v>269</v>
       </c>
       <c r="Y20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Z20" t="s">
         <v>308</v>
       </c>
       <c r="AA20">
-        <v>0.99903141795748496</v>
+        <v>0.99815762041917688</v>
       </c>
       <c r="AB20">
-        <v>17.757337446108838</v>
+        <v>33.776958981757815</v>
       </c>
       <c r="AD20" t="s">
         <v>248</v>
@@ -8212,10 +8212,10 @@
         <v>385</v>
       </c>
       <c r="AO20">
-        <v>0.99838078830661203</v>
+        <v>0.99664078053750105</v>
       </c>
       <c r="AP20">
-        <v>29.68554771211182</v>
+        <v>61.585690145814638</v>
       </c>
       <c r="AR20" t="s">
         <v>248</v>
@@ -8316,16 +8316,16 @@
         <v>271</v>
       </c>
       <c r="Y21" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="Z21" t="s">
         <v>309</v>
       </c>
       <c r="AA21">
-        <v>0.99797139203037322</v>
+        <v>0.99887966592548594</v>
       </c>
       <c r="AB21">
-        <v>37.191146109824579</v>
+        <v>20.53945803275866</v>
       </c>
       <c r="AD21" t="s">
         <v>248</v>
@@ -8358,10 +8358,10 @@
         <v>387</v>
       </c>
       <c r="AO21">
-        <v>0.99852500850690518</v>
+        <v>0.99785502426144801</v>
       </c>
       <c r="AP21">
-        <v>27.041510706738034</v>
+        <v>39.324555206787501</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8426,16 +8426,16 @@
         <v>273</v>
       </c>
       <c r="Y22" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s">
         <v>310</v>
       </c>
       <c r="AA22">
-        <v>0.99872758352859059</v>
+        <v>0.99828989494874287</v>
       </c>
       <c r="AB22">
-        <v>23.327635309172347</v>
+        <v>31.351925939714036</v>
       </c>
       <c r="AD22" t="s">
         <v>248</v>
@@ -8468,10 +8468,10 @@
         <v>389</v>
       </c>
       <c r="AO22">
-        <v>0.99753724381235709</v>
+        <v>0.99667925950575054</v>
       </c>
       <c r="AP22">
-        <v>45.150530106787691</v>
+        <v>60.880242394574381</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8536,16 +8536,16 @@
         <v>275</v>
       </c>
       <c r="Y23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
         <v>311</v>
       </c>
       <c r="AA23">
-        <v>0.99786441593591435</v>
+        <v>0.99831420288554851</v>
       </c>
       <c r="AB23">
-        <v>39.152374508236058</v>
+        <v>30.906280431611009</v>
       </c>
       <c r="AD23" t="s">
         <v>248</v>
@@ -8578,10 +8578,10 @@
         <v>391</v>
       </c>
       <c r="AO23">
-        <v>0.99821483672858236</v>
+        <v>0.99888649626708259</v>
       </c>
       <c r="AP23">
-        <v>32.727993309323963</v>
+        <v>20.414235103486192</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8646,16 +8646,16 @@
         <v>277</v>
       </c>
       <c r="Y24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="s">
         <v>312</v>
       </c>
       <c r="AA24">
-        <v>0.9984521235218653</v>
+        <v>0.99905448261210317</v>
       </c>
       <c r="AB24">
-        <v>28.377735432469407</v>
+        <v>17.334485444775215</v>
       </c>
       <c r="AD24" t="s">
         <v>248</v>
@@ -8688,10 +8688,10 @@
         <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.99851446571821256</v>
+        <v>0.99888703680442148</v>
       </c>
       <c r="AP24">
-        <v>27.234795166103936</v>
+        <v>20.404325252272194</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8756,16 +8756,16 @@
         <v>279</v>
       </c>
       <c r="Y25" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s">
         <v>313</v>
       </c>
       <c r="AA25">
-        <v>0.99905448261210317</v>
+        <v>0.99845115321674904</v>
       </c>
       <c r="AB25">
-        <v>17.334485444775215</v>
+        <v>28.395524359600802</v>
       </c>
       <c r="AD25" t="s">
         <v>248</v>
@@ -8798,10 +8798,10 @@
         <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.99853436339984547</v>
+        <v>0.99851437709898627</v>
       </c>
       <c r="AP25">
-        <v>26.870004336166144</v>
+        <v>27.236419851917539</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8866,16 +8866,16 @@
         <v>281</v>
       </c>
       <c r="Y26" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="Z26" t="s">
         <v>314</v>
       </c>
       <c r="AA26">
-        <v>0.99845115321674904</v>
+        <v>0.99792185696155833</v>
       </c>
       <c r="AB26">
-        <v>28.395524359600802</v>
+        <v>38.099289038098078</v>
       </c>
       <c r="AD26" t="s">
         <v>248</v>
@@ -8908,10 +8908,10 @@
         <v>397</v>
       </c>
       <c r="AO26">
-        <v>0.99785502426144801</v>
+        <v>0.99835510064157384</v>
       </c>
       <c r="AP26">
-        <v>39.324555206787501</v>
+        <v>30.156488237812564</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8976,16 +8976,16 @@
         <v>283</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="Z27" t="s">
         <v>315</v>
       </c>
       <c r="AA27">
-        <v>0.99792185696155833</v>
+        <v>0.99783379528973448</v>
       </c>
       <c r="AB27">
-        <v>38.099289038098078</v>
+        <v>39.713753021534231</v>
       </c>
       <c r="AD27" t="s">
         <v>248</v>
@@ -9018,10 +9018,10 @@
         <v>399</v>
       </c>
       <c r="AO27">
-        <v>0.99667925950575054</v>
+        <v>0.99853436339984547</v>
       </c>
       <c r="AP27">
-        <v>60.880242394574381</v>
+        <v>26.870004336166144</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9086,16 +9086,16 @@
         <v>285</v>
       </c>
       <c r="Y28" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="Z28" t="s">
         <v>316</v>
       </c>
       <c r="AA28">
-        <v>0.99783379528973448</v>
+        <v>0.99852845242200794</v>
       </c>
       <c r="AB28">
-        <v>39.713753021534231</v>
+        <v>26.978372263188255</v>
       </c>
       <c r="AD28" t="s">
         <v>248</v>
@@ -9128,10 +9128,10 @@
         <v>401</v>
       </c>
       <c r="AO28">
-        <v>0.99664078053750105</v>
+        <v>0.9985540071847413</v>
       </c>
       <c r="AP28">
-        <v>61.585690145814638</v>
+        <v>26.509868279743756</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9196,16 +9196,16 @@
         <v>287</v>
       </c>
       <c r="Y29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Z29" t="s">
         <v>317</v>
       </c>
       <c r="AA29">
-        <v>0.99852845242200794</v>
+        <v>0.99876909403276848</v>
       </c>
       <c r="AB29">
-        <v>26.978372263188255</v>
+        <v>22.56660939924376</v>
       </c>
       <c r="AD29" t="s">
         <v>248</v>
@@ -9238,10 +9238,10 @@
         <v>403</v>
       </c>
       <c r="AO29">
-        <v>0.99888649626708259</v>
+        <v>0.99912192348268269</v>
       </c>
       <c r="AP29">
-        <v>20.414235103486192</v>
+        <v>16.098069484150571</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9306,16 +9306,16 @@
         <v>289</v>
       </c>
       <c r="Y30" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s">
         <v>318</v>
       </c>
       <c r="AA30">
-        <v>0.99876909403276848</v>
+        <v>0.99786441593591435</v>
       </c>
       <c r="AB30">
-        <v>22.56660939924376</v>
+        <v>39.152374508236058</v>
       </c>
       <c r="AD30" t="s">
         <v>248</v>
@@ -9348,10 +9348,10 @@
         <v>405</v>
       </c>
       <c r="AO30">
-        <v>0.99888703680442148</v>
+        <v>0.99864092836530338</v>
       </c>
       <c r="AP30">
-        <v>20.404325252272194</v>
+        <v>24.916313302771705</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9416,16 +9416,16 @@
         <v>291</v>
       </c>
       <c r="Y31" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="Z31" t="s">
         <v>319</v>
       </c>
       <c r="AA31">
-        <v>0.99887966592548594</v>
+        <v>0.9982564657516575</v>
       </c>
       <c r="AB31">
-        <v>20.53945803275866</v>
+        <v>31.964794552945094</v>
       </c>
       <c r="AD31" t="s">
         <v>248</v>
@@ -9458,10 +9458,10 @@
         <v>407</v>
       </c>
       <c r="AO31">
-        <v>0.99851437709898627</v>
+        <v>0.99840287720275267</v>
       </c>
       <c r="AP31">
-        <v>27.236419851917539</v>
+        <v>29.280584616200382</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9526,16 +9526,16 @@
         <v>293</v>
       </c>
       <c r="Y32" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Z32" t="s">
         <v>320</v>
       </c>
       <c r="AA32">
-        <v>0.99828989494874287</v>
+        <v>0.99854052945036897</v>
       </c>
       <c r="AB32">
-        <v>31.351925939714036</v>
+        <v>26.756960076568774</v>
       </c>
       <c r="AD32" t="s">
         <v>248</v>
@@ -9568,10 +9568,10 @@
         <v>409</v>
       </c>
       <c r="AO32">
-        <v>0.99835510064157384</v>
+        <v>0.99798110605540413</v>
       </c>
       <c r="AP32">
-        <v>30.156488237812564</v>
+        <v>37.013055650923285</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9636,16 +9636,16 @@
         <v>295</v>
       </c>
       <c r="Y33" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Z33" t="s">
         <v>321</v>
       </c>
       <c r="AA33">
-        <v>0.99831420288554851</v>
+        <v>0.99783818599396734</v>
       </c>
       <c r="AB33">
-        <v>30.906280431611009</v>
+        <v>39.633256777265125</v>
       </c>
     </row>
   </sheetData>
@@ -9654,7 +9654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF1CA77-FD6E-44A2-9203-AFE49F62FD7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAE6A36-8EE7-40B6-A91A-508BB84719A1}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9766,7 +9766,7 @@
         <v>449</v>
       </c>
       <c r="K11" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L11">
         <v>79.362778177778793</v>
@@ -9799,7 +9799,7 @@
         <v>493</v>
       </c>
       <c r="X11" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="Y11">
         <v>108.8275</v>
@@ -9834,7 +9834,7 @@
         <v>451</v>
       </c>
       <c r="K12" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="L12">
         <v>50.354564381123943</v>
@@ -9867,7 +9867,7 @@
         <v>495</v>
       </c>
       <c r="X12" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="Y12">
         <v>54.292499999999997</v>
@@ -9902,7 +9902,7 @@
         <v>453</v>
       </c>
       <c r="K13" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="L13">
         <v>57.005439523831519</v>
@@ -9935,7 +9935,7 @@
         <v>497</v>
       </c>
       <c r="X13" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="Y13">
         <v>50.356250000000003</v>
@@ -9970,7 +9970,7 @@
         <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L14">
         <v>19.895723562817633</v>
@@ -10003,7 +10003,7 @@
         <v>499</v>
       </c>
       <c r="X14" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="Y14">
         <v>9.5987500000000008</v>
@@ -10038,7 +10038,7 @@
         <v>457</v>
       </c>
       <c r="K15" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="L15">
         <v>9.5699994650614961</v>
@@ -10071,7 +10071,7 @@
         <v>501</v>
       </c>
       <c r="X15" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="Y15">
         <v>50.66</v>
@@ -10106,7 +10106,7 @@
         <v>459</v>
       </c>
       <c r="K16" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="L16">
         <v>44.760252416795389</v>
@@ -10139,7 +10139,7 @@
         <v>503</v>
       </c>
       <c r="X16" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="Y16">
         <v>5.0000000000000001E-3</v>
@@ -10174,7 +10174,7 @@
         <v>461</v>
       </c>
       <c r="K17" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="L17">
         <v>40.59880776523103</v>
@@ -10242,7 +10242,7 @@
         <v>463</v>
       </c>
       <c r="K18" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="L18">
         <v>71.045385513132985</v>
@@ -10275,7 +10275,7 @@
         <v>507</v>
       </c>
       <c r="X18" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="Y18">
         <v>7.5287499999999996</v>
@@ -10310,7 +10310,7 @@
         <v>465</v>
       </c>
       <c r="K19" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="L19">
         <v>63.055598832310729</v>
@@ -10343,7 +10343,7 @@
         <v>509</v>
       </c>
       <c r="X19" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="Y19">
         <v>14.6</v>
@@ -10378,7 +10378,7 @@
         <v>467</v>
       </c>
       <c r="K20" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="L20">
         <v>43.89469200396065</v>
@@ -10411,7 +10411,7 @@
         <v>511</v>
       </c>
       <c r="X20" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="Y20">
         <v>0.24374999999999999</v>
@@ -10446,7 +10446,7 @@
         <v>469</v>
       </c>
       <c r="K21" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="L21">
         <v>11.547936358898198</v>
@@ -10481,7 +10481,7 @@
         <v>471</v>
       </c>
       <c r="K22" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="L22">
         <v>31.481356456094364</v>
@@ -10516,7 +10516,7 @@
         <v>473</v>
       </c>
       <c r="K23" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="L23">
         <v>15.708789779919334</v>
@@ -10551,7 +10551,7 @@
         <v>475</v>
       </c>
       <c r="K24" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="L24">
         <v>20.814752751471318</v>
@@ -10586,7 +10586,7 @@
         <v>477</v>
       </c>
       <c r="K25" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L25">
         <v>50.266717026070005</v>
@@ -10621,7 +10621,7 @@
         <v>479</v>
       </c>
       <c r="K26" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="L26">
         <v>56.728889145623882</v>
@@ -10656,7 +10656,7 @@
         <v>481</v>
       </c>
       <c r="K27" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="L27">
         <v>70.602917671125681</v>
@@ -10691,7 +10691,7 @@
         <v>483</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="L28">
         <v>7.8153674765988201</v>
@@ -10726,7 +10726,7 @@
         <v>485</v>
       </c>
       <c r="K29" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="L29">
         <v>26.861604762024118</v>
@@ -10761,7 +10761,7 @@
         <v>487</v>
       </c>
       <c r="K30" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="L30">
         <v>10.889866530825216</v>
@@ -10796,7 +10796,7 @@
         <v>489</v>
       </c>
       <c r="K31" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="L31">
         <v>9.0084683548455349</v>
@@ -10831,7 +10831,7 @@
         <v>491</v>
       </c>
       <c r="K32" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="L32">
         <v>35.009005865752776</v>
@@ -10846,7 +10846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE09647-8E14-41F2-A267-0B4C48C22828}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0BC68A-F8D8-474F-9BA7-7DF855ABC0AA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12663,7 +12663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190BFF03-6938-4FC1-8AE8-3525C977883D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267ECB01-5A42-47A2-92B6-02653841496A}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9DA179C-5B83-4635-89E4-1C2031611E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11F7C79D-7188-4C9A-9CCE-30016BEEAD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -877,18 +877,36 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_017</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_013</t>
   </si>
   <si>
@@ -901,108 +919,96 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_005</t>
   </si>
   <si>
@@ -1015,18 +1021,21 @@
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_DE118-380,e_DE69-380,e_w33816726-380,e_DE87-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
+  </si>
+  <si>
+    <t>e_w1072574879-380,e_w30622610-380,e_DE20-380,e_w11285720-380,e_w25306938-380,e_w28343121-380,e_w1089911133-380,e_w1102237380-380,e_w30040568-380,e_w275466323</t>
+  </si>
+  <si>
+    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
+  </si>
+  <si>
     <t>e_w1024536785-380,e_w26593929-380,e_DE159-380,e_w26777313-380,e_w160584794-380,e_w152403632-380,e_w38661452-380,e_DE157-380</t>
   </si>
   <si>
@@ -1036,64 +1045,157 @@
     <t>e_w797009308-380,e_w1128250704-380,e_w883928229-380,e_w951773852-380,e_w32076853-380,e_w955268864-380</t>
   </si>
   <si>
+    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380,e_w24976300-380,e_DE183-380</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
+  </si>
+  <si>
+    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
+  </si>
+  <si>
+    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
+  </si>
+  <si>
+    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
+  </si>
+  <si>
+    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
+  </si>
+  <si>
+    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
+  </si>
+  <si>
+    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
+  </si>
+  <si>
+    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
+  </si>
+  <si>
+    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
+  </si>
+  <si>
+    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
+  </si>
+  <si>
+    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
+  </si>
+  <si>
+    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
+  </si>
+  <si>
     <t>e_w5404079-380,e_w26245195-380,e_w24976300-380</t>
   </si>
   <si>
-    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
-  </si>
-  <si>
-    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
-  </si>
-  <si>
-    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
-  </si>
-  <si>
-    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
-  </si>
-  <si>
-    <t>e_DE118-380,e_DE69-380,e_w33816726-380,e_DE87-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
-  </si>
-  <si>
-    <t>e_w1072574879-380,e_w30622610-380,e_DE20-380,e_w11285720-380,e_w25306938-380,e_w28343121-380,e_w1089911133-380,e_w1102237380-380,e_w30040568-380,e_w275466323</t>
-  </si>
-  <si>
-    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
-  </si>
-  <si>
-    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
-  </si>
-  <si>
-    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
-  </si>
-  <si>
-    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
-  </si>
-  <si>
-    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
-  </si>
-  <si>
-    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
-  </si>
-  <si>
-    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
-  </si>
-  <si>
     <t>e_w31131325-380,e_w25306752-380,e_w31131320-380,e_w41389594-380,e_w57727004-380,e_w683227471-380,e_w88945213-380,e_DE240-380,e_w30613895-380,e_w53378027-380</t>
   </si>
   <si>
     <t>e_w947118608-380,e_w941453716-380,e_w30039908-380,e_w1091984573-380,e_DE21-400,e_w943444232-380</t>
   </si>
   <si>
-    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380,e_w24976300-380,e_DE183-380</t>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -1114,40 +1216,10 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1156,76 +1228,106 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w941453716-380,e_w1091984573-380,e_w943444232-380</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w1024536785-380,e_w26593929-380,e_DE118-380,e_DE69-380,e_DE159-380,e_w26777313-380,e_w33816726-380,e_DE87-380,e_w152403632-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w87653464-380,e_w87653464-400,e_w42049947-380,e_w26814283-380,e_w152261133-380,e_DE217-380,e_DE202-380</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w143903369-380,e_w55069713-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w24705761-380,e_w24758329-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w26404600-380,e_w26403575-380,e_w88945213-380,e_w38325076-380,e_w53378027-380,e_w76246159-380</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w24976300-380</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380,e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w88901626-380,e_w31367940-380</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w160584794-380,e_w38661452-380,e_DE157-380,e_w42372159-380,e_w156673636-380,e_DE121-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w951773852-380,e_w27739871-380,e_w955268864-380,e_w1072574879-380,e_w23899043-380,e_DE20-380,e_w11285720-380,e_w24262656-380,e_w28343121-380,e_w1089911133-380,e_w26474759-380,e_w30040568-380</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w25306752-380,e_w41389594-380</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w683227471-380,e_w30613895-380</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -1246,40 +1348,10 @@
     <t>e_DE23-380,e_w797009308-380,e_w1280178911-380,e_w1128250704-380,e_w883928229-380,e_w31024391-380,e_w32076853-380,e_w603661085-380,e_w946969736-380</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w941453716-380,e_w1091984573-380,e_w943444232-380</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w683227471-380,e_w30613895-380</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -1288,76 +1360,28 @@
     <t>e_w26245195-380,e_w24976300-380</t>
   </si>
   <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w24976300-380</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w1024536785-380,e_w26593929-380,e_DE118-380,e_DE69-380,e_DE159-380,e_w26777313-380,e_w33816726-380,e_DE87-380,e_w152403632-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w87653464-380,e_w87653464-400,e_w42049947-380,e_w26814283-380,e_w152261133-380,e_DE217-380,e_DE202-380</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w143903369-380,e_w55069713-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w24705761-380,e_w24758329-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w26404600-380,e_w26403575-380,e_w88945213-380,e_w38325076-380,e_w53378027-380,e_w76246159-380</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380,e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w88901626-380,e_w31367940-380</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w160584794-380,e_w38661452-380,e_DE157-380,e_w42372159-380,e_w156673636-380,e_DE121-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w951773852-380,e_w27739871-380,e_w955268864-380,e_w1072574879-380,e_w23899043-380,e_DE20-380,e_w11285720-380,e_w24262656-380,e_w28343121-380,e_w1089911133-380,e_w26474759-380,e_w30040568-380</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w25306752-380,e_w41389594-380</t>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_009</t>
@@ -1378,46 +1402,46 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w1280178911-380</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w883768276-380,e_w1134105414-380</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w941453716-380,e_w1091984573-380</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_DE21-400</t>
   </si>
   <si>
     <t>elc_wof_009</t>
@@ -1438,43 +1462,19 @@
     <t>e_w275466323,e_w234171369-380</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w829116805-380,e_w289836713-380,e_DE16-380,e_DE13-380</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
-    <t>e_DE23-380,e_w1280178911-380</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_DE23-380,e_w883768276-380,e_w1134105414-380</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w941453716-380,e_w1091984573-380</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_DE21-400</t>
-  </si>
-  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
     <t>e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w829116805-380,e_w289836713-380,e_DE16-380,e_DE13-380</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6618,7 +6618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8748A45D-1393-40CC-A1D0-AC511BEE902A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6C4863-F4A9-4E9A-B189-FA7B94A98094}">
   <dimension ref="B9:BD33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6856,16 +6856,16 @@
         <v>249</v>
       </c>
       <c r="Y11" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Z11" t="s">
         <v>299</v>
       </c>
       <c r="AA11">
-        <v>0.99903141795748496</v>
+        <v>0.99902896095987681</v>
       </c>
       <c r="AB11">
-        <v>17.757337446108838</v>
+        <v>17.802382402257905</v>
       </c>
       <c r="AD11" t="s">
         <v>248</v>
@@ -6898,10 +6898,10 @@
         <v>367</v>
       </c>
       <c r="AO11">
-        <v>0.99821483672858236</v>
+        <v>0.99753724381235709</v>
       </c>
       <c r="AP11">
-        <v>32.727993309323963</v>
+        <v>45.150530106787691</v>
       </c>
       <c r="AR11" t="s">
         <v>248</v>
@@ -6934,10 +6934,10 @@
         <v>431</v>
       </c>
       <c r="BC11">
-        <v>0.99726555940500838</v>
+        <v>0.99374840656294539</v>
       </c>
       <c r="BD11">
-        <v>50.131410908180094</v>
+        <v>114.61254634600208</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7002,16 +7002,16 @@
         <v>253</v>
       </c>
       <c r="Y12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z12" t="s">
         <v>300</v>
       </c>
       <c r="AA12">
-        <v>0.99797139203037322</v>
+        <v>0.99815762041917688</v>
       </c>
       <c r="AB12">
-        <v>37.191146109824579</v>
+        <v>33.776958981757815</v>
       </c>
       <c r="AD12" t="s">
         <v>248</v>
@@ -7044,10 +7044,10 @@
         <v>369</v>
       </c>
       <c r="AO12">
-        <v>0.99851446571821256</v>
+        <v>0.99831023082457615</v>
       </c>
       <c r="AP12">
-        <v>27.234795166103936</v>
+        <v>30.979101549436738</v>
       </c>
       <c r="AR12" t="s">
         <v>248</v>
@@ -7080,10 +7080,10 @@
         <v>433</v>
       </c>
       <c r="BC12">
-        <v>0.99345136660650646</v>
+        <v>0.99731983040343442</v>
       </c>
       <c r="BD12">
-        <v>120.05827888071518</v>
+        <v>49.136442603701539</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7148,16 +7148,16 @@
         <v>255</v>
       </c>
       <c r="Y13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z13" t="s">
         <v>301</v>
       </c>
       <c r="AA13">
-        <v>0.99872758352859059</v>
+        <v>0.99786441593591435</v>
       </c>
       <c r="AB13">
-        <v>23.327635309172347</v>
+        <v>39.152374508236058</v>
       </c>
       <c r="AD13" t="s">
         <v>248</v>
@@ -7190,10 +7190,10 @@
         <v>371</v>
       </c>
       <c r="AO13">
-        <v>0.9982655473126083</v>
+        <v>0.99888649626708259</v>
       </c>
       <c r="AP13">
-        <v>31.798299268848115</v>
+        <v>20.414235103486192</v>
       </c>
       <c r="AR13" t="s">
         <v>248</v>
@@ -7226,10 +7226,10 @@
         <v>435</v>
       </c>
       <c r="BC13">
-        <v>0.99861480954449533</v>
+        <v>0.9955056076869333</v>
       </c>
       <c r="BD13">
-        <v>25.395158350918766</v>
+        <v>82.397192406223127</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7294,16 +7294,16 @@
         <v>257</v>
       </c>
       <c r="Y14" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="Z14" t="s">
         <v>302</v>
       </c>
       <c r="AA14">
-        <v>0.9966615805732193</v>
+        <v>0.99903141795748496</v>
       </c>
       <c r="AB14">
-        <v>61.204356157646131</v>
+        <v>17.757337446108838</v>
       </c>
       <c r="AD14" t="s">
         <v>248</v>
@@ -7336,10 +7336,10 @@
         <v>373</v>
       </c>
       <c r="AO14">
-        <v>0.99753724381235709</v>
+        <v>0.99888703680442148</v>
       </c>
       <c r="AP14">
-        <v>45.150530106787691</v>
+        <v>20.404325252272194</v>
       </c>
       <c r="AR14" t="s">
         <v>248</v>
@@ -7372,10 +7372,10 @@
         <v>437</v>
       </c>
       <c r="BC14">
-        <v>0.98635566783526007</v>
+        <v>0.99845350558031343</v>
       </c>
       <c r="BD14">
-        <v>250.14608968689959</v>
+        <v>28.352397694253892</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7440,16 +7440,16 @@
         <v>259</v>
       </c>
       <c r="Y15" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="Z15" t="s">
         <v>303</v>
       </c>
       <c r="AA15">
-        <v>0.9984521235218653</v>
+        <v>0.99797139203037322</v>
       </c>
       <c r="AB15">
-        <v>28.377735432469407</v>
+        <v>37.191146109824579</v>
       </c>
       <c r="AD15" t="s">
         <v>248</v>
@@ -7482,10 +7482,10 @@
         <v>375</v>
       </c>
       <c r="AO15">
-        <v>0.99831023082457615</v>
+        <v>0.99851437709898627</v>
       </c>
       <c r="AP15">
-        <v>30.979101549436738</v>
+        <v>27.236419851917539</v>
       </c>
       <c r="AR15" t="s">
         <v>248</v>
@@ -7515,13 +7515,13 @@
         <v>438</v>
       </c>
       <c r="BB15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="BC15">
-        <v>0.99374840656294539</v>
+        <v>0.99726555940500838</v>
       </c>
       <c r="BD15">
-        <v>114.61254634600208</v>
+        <v>50.131410908180094</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7586,16 +7586,16 @@
         <v>261</v>
       </c>
       <c r="Y16" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Z16" t="s">
         <v>304</v>
       </c>
       <c r="AA16">
-        <v>0.99837540256192037</v>
+        <v>0.99872758352859059</v>
       </c>
       <c r="AB16">
-        <v>29.784286364794184</v>
+        <v>23.327635309172347</v>
       </c>
       <c r="AD16" t="s">
         <v>248</v>
@@ -7628,10 +7628,10 @@
         <v>377</v>
       </c>
       <c r="AO16">
-        <v>0.99810796133130941</v>
+        <v>0.99835510064157384</v>
       </c>
       <c r="AP16">
-        <v>34.687375592660409</v>
+        <v>30.156488237812564</v>
       </c>
       <c r="AR16" t="s">
         <v>248</v>
@@ -7658,16 +7658,16 @@
         <v>420</v>
       </c>
       <c r="BA16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="BB16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BC16">
-        <v>0.99731983040343442</v>
+        <v>0.99345136660650646</v>
       </c>
       <c r="BD16">
-        <v>49.136442603701539</v>
+        <v>120.05827888071518</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7732,16 +7732,16 @@
         <v>263</v>
       </c>
       <c r="Y17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s">
         <v>305</v>
       </c>
       <c r="AA17">
-        <v>0.99839933473711795</v>
+        <v>0.99783818599396734</v>
       </c>
       <c r="AB17">
-        <v>29.345529819503312</v>
+        <v>39.633256777265125</v>
       </c>
       <c r="AD17" t="s">
         <v>248</v>
@@ -7774,10 +7774,10 @@
         <v>379</v>
       </c>
       <c r="AO17">
-        <v>0.99798114961534334</v>
+        <v>0.99785502426144801</v>
       </c>
       <c r="AP17">
-        <v>37.012257052039594</v>
+        <v>39.324555206787501</v>
       </c>
       <c r="AR17" t="s">
         <v>248</v>
@@ -7804,16 +7804,16 @@
         <v>422</v>
       </c>
       <c r="BA17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="BB17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="BC17">
-        <v>0.9955056076869333</v>
+        <v>0.99861480954449533</v>
       </c>
       <c r="BD17">
-        <v>82.397192406223127</v>
+        <v>25.395158350918766</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7878,16 +7878,16 @@
         <v>265</v>
       </c>
       <c r="Y18" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z18" t="s">
         <v>306</v>
       </c>
       <c r="AA18">
-        <v>0.9981906651950686</v>
+        <v>0.99905448261210317</v>
       </c>
       <c r="AB18">
-        <v>33.171138090409563</v>
+        <v>17.334485444775215</v>
       </c>
       <c r="AD18" t="s">
         <v>248</v>
@@ -7920,10 +7920,10 @@
         <v>381</v>
       </c>
       <c r="AO18">
-        <v>0.99838078830661203</v>
+        <v>0.99667925950575054</v>
       </c>
       <c r="AP18">
-        <v>29.68554771211182</v>
+        <v>60.880242394574381</v>
       </c>
       <c r="AR18" t="s">
         <v>248</v>
@@ -7950,16 +7950,16 @@
         <v>424</v>
       </c>
       <c r="BA18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BB18" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BC18">
-        <v>0.99845350558031343</v>
+        <v>0.99871075555058875</v>
       </c>
       <c r="BD18">
-        <v>28.352397694253892</v>
+        <v>23.636148239206339</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8024,16 +8024,16 @@
         <v>267</v>
       </c>
       <c r="Y19" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="Z19" t="s">
         <v>307</v>
       </c>
       <c r="AA19">
-        <v>0.99902896095987681</v>
+        <v>0.99845115321674904</v>
       </c>
       <c r="AB19">
-        <v>17.802382402257905</v>
+        <v>28.395524359600802</v>
       </c>
       <c r="AD19" t="s">
         <v>248</v>
@@ -8066,10 +8066,10 @@
         <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.99852500850690518</v>
+        <v>0.9985540071847413</v>
       </c>
       <c r="AP19">
-        <v>27.041510706738034</v>
+        <v>26.509868279743756</v>
       </c>
       <c r="AR19" t="s">
         <v>248</v>
@@ -8096,16 +8096,16 @@
         <v>426</v>
       </c>
       <c r="BA19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="BB19" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="BC19">
-        <v>0.99733561350881073</v>
+        <v>0.98635566783526007</v>
       </c>
       <c r="BD19">
-        <v>48.847085671804372</v>
+        <v>250.14608968689959</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8170,16 +8170,16 @@
         <v>269</v>
       </c>
       <c r="Y20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z20" t="s">
         <v>308</v>
       </c>
       <c r="AA20">
-        <v>0.99815762041917688</v>
+        <v>0.99792185696155833</v>
       </c>
       <c r="AB20">
-        <v>33.776958981757815</v>
+        <v>38.099289038098078</v>
       </c>
       <c r="AD20" t="s">
         <v>248</v>
@@ -8212,10 +8212,10 @@
         <v>385</v>
       </c>
       <c r="AO20">
-        <v>0.99664078053750105</v>
+        <v>0.99912192348268269</v>
       </c>
       <c r="AP20">
-        <v>61.585690145814638</v>
+        <v>16.098069484150571</v>
       </c>
       <c r="AR20" t="s">
         <v>248</v>
@@ -8248,10 +8248,10 @@
         <v>448</v>
       </c>
       <c r="BC20">
-        <v>0.99871075555058875</v>
+        <v>0.99733561350881073</v>
       </c>
       <c r="BD20">
-        <v>23.636148239206339</v>
+        <v>48.847085671804372</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8316,16 +8316,16 @@
         <v>271</v>
       </c>
       <c r="Y21" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="Z21" t="s">
         <v>309</v>
       </c>
       <c r="AA21">
-        <v>0.99887966592548594</v>
+        <v>0.99783379528973448</v>
       </c>
       <c r="AB21">
-        <v>20.53945803275866</v>
+        <v>39.713753021534231</v>
       </c>
       <c r="AD21" t="s">
         <v>248</v>
@@ -8358,10 +8358,10 @@
         <v>387</v>
       </c>
       <c r="AO21">
-        <v>0.99785502426144801</v>
+        <v>0.99864092836530338</v>
       </c>
       <c r="AP21">
-        <v>39.324555206787501</v>
+        <v>24.916313302771705</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8426,16 +8426,16 @@
         <v>273</v>
       </c>
       <c r="Y22" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Z22" t="s">
         <v>310</v>
       </c>
       <c r="AA22">
-        <v>0.99828989494874287</v>
+        <v>0.99852845242200794</v>
       </c>
       <c r="AB22">
-        <v>31.351925939714036</v>
+        <v>26.978372263188255</v>
       </c>
       <c r="AD22" t="s">
         <v>248</v>
@@ -8468,10 +8468,10 @@
         <v>389</v>
       </c>
       <c r="AO22">
-        <v>0.99667925950575054</v>
+        <v>0.99840287720275267</v>
       </c>
       <c r="AP22">
-        <v>60.880242394574381</v>
+        <v>29.280584616200382</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8536,16 +8536,16 @@
         <v>275</v>
       </c>
       <c r="Y23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s">
         <v>311</v>
       </c>
       <c r="AA23">
-        <v>0.99831420288554851</v>
+        <v>0.99876909403276848</v>
       </c>
       <c r="AB23">
-        <v>30.906280431611009</v>
+        <v>22.56660939924376</v>
       </c>
       <c r="AD23" t="s">
         <v>248</v>
@@ -8578,10 +8578,10 @@
         <v>391</v>
       </c>
       <c r="AO23">
-        <v>0.99888649626708259</v>
+        <v>0.99798110605540413</v>
       </c>
       <c r="AP23">
-        <v>20.414235103486192</v>
+        <v>37.013055650923285</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8646,16 +8646,16 @@
         <v>277</v>
       </c>
       <c r="Y24" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s">
         <v>312</v>
       </c>
       <c r="AA24">
-        <v>0.99905448261210317</v>
+        <v>0.9984521235218653</v>
       </c>
       <c r="AB24">
-        <v>17.334485444775215</v>
+        <v>28.377735432469407</v>
       </c>
       <c r="AD24" t="s">
         <v>248</v>
@@ -8688,10 +8688,10 @@
         <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.99888703680442148</v>
+        <v>0.99810796133130941</v>
       </c>
       <c r="AP24">
-        <v>20.404325252272194</v>
+        <v>34.687375592660409</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8756,16 +8756,16 @@
         <v>279</v>
       </c>
       <c r="Y25" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="Z25" t="s">
         <v>313</v>
       </c>
       <c r="AA25">
-        <v>0.99845115321674904</v>
+        <v>0.99837540256192037</v>
       </c>
       <c r="AB25">
-        <v>28.395524359600802</v>
+        <v>29.784286364794184</v>
       </c>
       <c r="AD25" t="s">
         <v>248</v>
@@ -8798,10 +8798,10 @@
         <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.99851437709898627</v>
+        <v>0.99798114961534334</v>
       </c>
       <c r="AP25">
-        <v>27.236419851917539</v>
+        <v>37.012257052039594</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8866,16 +8866,16 @@
         <v>281</v>
       </c>
       <c r="Y26" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="Z26" t="s">
         <v>314</v>
       </c>
       <c r="AA26">
-        <v>0.99792185696155833</v>
+        <v>0.99839933473711795</v>
       </c>
       <c r="AB26">
-        <v>38.099289038098078</v>
+        <v>29.345529819503312</v>
       </c>
       <c r="AD26" t="s">
         <v>248</v>
@@ -8908,10 +8908,10 @@
         <v>397</v>
       </c>
       <c r="AO26">
-        <v>0.99835510064157384</v>
+        <v>0.99838078830661203</v>
       </c>
       <c r="AP26">
-        <v>30.156488237812564</v>
+        <v>29.68554771211182</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8976,16 +8976,16 @@
         <v>283</v>
       </c>
       <c r="Y27" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="Z27" t="s">
         <v>315</v>
       </c>
       <c r="AA27">
-        <v>0.99783379528973448</v>
+        <v>0.99887966592548594</v>
       </c>
       <c r="AB27">
-        <v>39.713753021534231</v>
+        <v>20.53945803275866</v>
       </c>
       <c r="AD27" t="s">
         <v>248</v>
@@ -9018,10 +9018,10 @@
         <v>399</v>
       </c>
       <c r="AO27">
-        <v>0.99853436339984547</v>
+        <v>0.99852500850690518</v>
       </c>
       <c r="AP27">
-        <v>26.870004336166144</v>
+        <v>27.041510706738034</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9086,16 +9086,16 @@
         <v>285</v>
       </c>
       <c r="Y28" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Z28" t="s">
         <v>316</v>
       </c>
       <c r="AA28">
-        <v>0.99852845242200794</v>
+        <v>0.99828989494874287</v>
       </c>
       <c r="AB28">
-        <v>26.978372263188255</v>
+        <v>31.351925939714036</v>
       </c>
       <c r="AD28" t="s">
         <v>248</v>
@@ -9128,10 +9128,10 @@
         <v>401</v>
       </c>
       <c r="AO28">
-        <v>0.9985540071847413</v>
+        <v>0.99821483672858236</v>
       </c>
       <c r="AP28">
-        <v>26.509868279743756</v>
+        <v>32.727993309323963</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9196,16 +9196,16 @@
         <v>287</v>
       </c>
       <c r="Y29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z29" t="s">
         <v>317</v>
       </c>
       <c r="AA29">
-        <v>0.99876909403276848</v>
+        <v>0.99831420288554851</v>
       </c>
       <c r="AB29">
-        <v>22.56660939924376</v>
+        <v>30.906280431611009</v>
       </c>
       <c r="AD29" t="s">
         <v>248</v>
@@ -9238,10 +9238,10 @@
         <v>403</v>
       </c>
       <c r="AO29">
-        <v>0.99912192348268269</v>
+        <v>0.99851446571821256</v>
       </c>
       <c r="AP29">
-        <v>16.098069484150571</v>
+        <v>27.234795166103936</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9306,16 +9306,16 @@
         <v>289</v>
       </c>
       <c r="Y30" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="Z30" t="s">
         <v>318</v>
       </c>
       <c r="AA30">
-        <v>0.99786441593591435</v>
+        <v>0.9981906651950686</v>
       </c>
       <c r="AB30">
-        <v>39.152374508236058</v>
+        <v>33.171138090409563</v>
       </c>
       <c r="AD30" t="s">
         <v>248</v>
@@ -9348,10 +9348,10 @@
         <v>405</v>
       </c>
       <c r="AO30">
-        <v>0.99864092836530338</v>
+        <v>0.9982655473126083</v>
       </c>
       <c r="AP30">
-        <v>24.916313302771705</v>
+        <v>31.798299268848115</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9416,16 +9416,16 @@
         <v>291</v>
       </c>
       <c r="Y31" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Z31" t="s">
         <v>319</v>
       </c>
       <c r="AA31">
-        <v>0.9982564657516575</v>
+        <v>0.9966615805732193</v>
       </c>
       <c r="AB31">
-        <v>31.964794552945094</v>
+        <v>61.204356157646131</v>
       </c>
       <c r="AD31" t="s">
         <v>248</v>
@@ -9458,10 +9458,10 @@
         <v>407</v>
       </c>
       <c r="AO31">
-        <v>0.99840287720275267</v>
+        <v>0.99853436339984547</v>
       </c>
       <c r="AP31">
-        <v>29.280584616200382</v>
+        <v>26.870004336166144</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9526,16 +9526,16 @@
         <v>293</v>
       </c>
       <c r="Y32" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Z32" t="s">
         <v>320</v>
       </c>
       <c r="AA32">
-        <v>0.99854052945036897</v>
+        <v>0.9982564657516575</v>
       </c>
       <c r="AB32">
-        <v>26.756960076568774</v>
+        <v>31.964794552945094</v>
       </c>
       <c r="AD32" t="s">
         <v>248</v>
@@ -9568,10 +9568,10 @@
         <v>409</v>
       </c>
       <c r="AO32">
-        <v>0.99798110605540413</v>
+        <v>0.99664078053750105</v>
       </c>
       <c r="AP32">
-        <v>37.013055650923285</v>
+        <v>61.585690145814638</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9636,16 +9636,16 @@
         <v>295</v>
       </c>
       <c r="Y33" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Z33" t="s">
         <v>321</v>
       </c>
       <c r="AA33">
-        <v>0.99783818599396734</v>
+        <v>0.99854052945036897</v>
       </c>
       <c r="AB33">
-        <v>39.633256777265125</v>
+        <v>26.756960076568774</v>
       </c>
     </row>
   </sheetData>
@@ -9654,7 +9654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAE6A36-8EE7-40B6-A91A-508BB84719A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47938EE7-7B41-4EC3-86FA-4D177D8351F9}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9766,7 +9766,7 @@
         <v>449</v>
       </c>
       <c r="K11" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="L11">
         <v>79.362778177778793</v>
@@ -9799,7 +9799,7 @@
         <v>493</v>
       </c>
       <c r="X11" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="Y11">
         <v>108.8275</v>
@@ -9834,7 +9834,7 @@
         <v>451</v>
       </c>
       <c r="K12" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="L12">
         <v>50.354564381123943</v>
@@ -9867,7 +9867,7 @@
         <v>495</v>
       </c>
       <c r="X12" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="Y12">
         <v>54.292499999999997</v>
@@ -9902,7 +9902,7 @@
         <v>453</v>
       </c>
       <c r="K13" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="L13">
         <v>57.005439523831519</v>
@@ -9935,7 +9935,7 @@
         <v>497</v>
       </c>
       <c r="X13" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="Y13">
         <v>50.356250000000003</v>
@@ -9970,7 +9970,7 @@
         <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="L14">
         <v>19.895723562817633</v>
@@ -10003,7 +10003,7 @@
         <v>499</v>
       </c>
       <c r="X14" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Y14">
         <v>9.5987500000000008</v>
@@ -10038,7 +10038,7 @@
         <v>457</v>
       </c>
       <c r="K15" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="L15">
         <v>9.5699994650614961</v>
@@ -10071,7 +10071,7 @@
         <v>501</v>
       </c>
       <c r="X15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Y15">
         <v>50.66</v>
@@ -10106,7 +10106,7 @@
         <v>459</v>
       </c>
       <c r="K16" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="L16">
         <v>44.760252416795389</v>
@@ -10139,7 +10139,7 @@
         <v>503</v>
       </c>
       <c r="X16" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="Y16">
         <v>5.0000000000000001E-3</v>
@@ -10174,7 +10174,7 @@
         <v>461</v>
       </c>
       <c r="K17" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="L17">
         <v>40.59880776523103</v>
@@ -10207,7 +10207,7 @@
         <v>505</v>
       </c>
       <c r="X17" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="Y17">
         <v>0.92625000000000002</v>
@@ -10242,7 +10242,7 @@
         <v>463</v>
       </c>
       <c r="K18" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="L18">
         <v>71.045385513132985</v>
@@ -10275,7 +10275,7 @@
         <v>507</v>
       </c>
       <c r="X18" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Y18">
         <v>7.5287499999999996</v>
@@ -10310,7 +10310,7 @@
         <v>465</v>
       </c>
       <c r="K19" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="L19">
         <v>63.055598832310729</v>
@@ -10343,7 +10343,7 @@
         <v>509</v>
       </c>
       <c r="X19" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="Y19">
         <v>14.6</v>
@@ -10378,7 +10378,7 @@
         <v>467</v>
       </c>
       <c r="K20" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="L20">
         <v>43.89469200396065</v>
@@ -10411,7 +10411,7 @@
         <v>511</v>
       </c>
       <c r="X20" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="Y20">
         <v>0.24374999999999999</v>
@@ -10446,7 +10446,7 @@
         <v>469</v>
       </c>
       <c r="K21" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="L21">
         <v>11.547936358898198</v>
@@ -10481,7 +10481,7 @@
         <v>471</v>
       </c>
       <c r="K22" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="L22">
         <v>31.481356456094364</v>
@@ -10516,7 +10516,7 @@
         <v>473</v>
       </c>
       <c r="K23" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="L23">
         <v>15.708789779919334</v>
@@ -10551,7 +10551,7 @@
         <v>475</v>
       </c>
       <c r="K24" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="L24">
         <v>20.814752751471318</v>
@@ -10586,7 +10586,7 @@
         <v>477</v>
       </c>
       <c r="K25" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="L25">
         <v>50.266717026070005</v>
@@ -10621,7 +10621,7 @@
         <v>479</v>
       </c>
       <c r="K26" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="L26">
         <v>56.728889145623882</v>
@@ -10656,7 +10656,7 @@
         <v>481</v>
       </c>
       <c r="K27" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="L27">
         <v>70.602917671125681</v>
@@ -10691,7 +10691,7 @@
         <v>483</v>
       </c>
       <c r="K28" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="L28">
         <v>7.8153674765988201</v>
@@ -10726,7 +10726,7 @@
         <v>485</v>
       </c>
       <c r="K29" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="L29">
         <v>26.861604762024118</v>
@@ -10761,7 +10761,7 @@
         <v>487</v>
       </c>
       <c r="K30" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="L30">
         <v>10.889866530825216</v>
@@ -10796,7 +10796,7 @@
         <v>489</v>
       </c>
       <c r="K31" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="L31">
         <v>9.0084683548455349</v>
@@ -10831,7 +10831,7 @@
         <v>491</v>
       </c>
       <c r="K32" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="L32">
         <v>35.009005865752776</v>
@@ -10846,7 +10846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0BC68A-F8D8-474F-9BA7-7DF855ABC0AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD0DC41-4694-45E5-A8D3-D3202134CF60}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12663,7 +12663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267ECB01-5A42-47A2-92B6-02653841496A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D0CB45-5525-406B-862E-9FDA9DCD8B64}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DEU_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11F7C79D-7188-4C9A-9CCE-30016BEEAD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74BAF2FB-8712-4D2A-B968-4D893D571081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -877,223 +877,265 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
+  </si>
+  <si>
+    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380,e_w24976300-380,e_DE183-380</t>
+  </si>
+  <si>
+    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
+  </si>
+  <si>
+    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
+  </si>
+  <si>
+    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
+  </si>
+  <si>
+    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
+  </si>
+  <si>
+    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
+  </si>
+  <si>
+    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
+  </si>
+  <si>
+    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
+  </si>
+  <si>
+    <t>e_w5404079-380,e_w26245195-380,e_w24976300-380</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
+  </si>
+  <si>
+    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
+  </si>
+  <si>
+    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
+  </si>
+  <si>
+    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
+  </si>
+  <si>
+    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
+  </si>
+  <si>
+    <t>e_w31131325-380,e_w25306752-380,e_w31131320-380,e_w41389594-380,e_w57727004-380,e_w683227471-380,e_w88945213-380,e_DE240-380,e_w30613895-380,e_w53378027-380</t>
+  </si>
+  <si>
+    <t>e_w947118608-380,e_w941453716-380,e_w30039908-380,e_w1091984573-380,e_DE21-400,e_w943444232-380</t>
+  </si>
+  <si>
+    <t>e_w1024536785-380,e_w26593929-380,e_DE159-380,e_w26777313-380,e_w160584794-380,e_w152403632-380,e_w38661452-380,e_DE157-380</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w1280178911-380,e_w31024391-380</t>
+  </si>
+  <si>
+    <t>e_w797009308-380,e_w1128250704-380,e_w883928229-380,e_w951773852-380,e_w32076853-380,e_w955268864-380</t>
+  </si>
+  <si>
     <t>e_DE118-380,e_DE69-380,e_w33816726-380,e_DE87-380,e_DE142-380,e_w42507488-380,e_w42799487-380,e_w42797575-380</t>
   </si>
   <si>
     <t>e_w1072574879-380,e_w30622610-380,e_DE20-380,e_w11285720-380,e_w25306938-380,e_w28343121-380,e_w1089911133-380,e_w1102237380-380,e_w30040568-380,e_w275466323</t>
   </si>
   <si>
-    <t>e_w234171369-380,e_DE8-380,e_w1094015892-380,e_w940919943,e_w941453716-380,e_w1091984573-380</t>
-  </si>
-  <si>
-    <t>e_w1024536785-380,e_w26593929-380,e_DE159-380,e_w26777313-380,e_w160584794-380,e_w152403632-380,e_w38661452-380,e_DE157-380</t>
-  </si>
-  <si>
-    <t>e_DE23-380,e_w1280178911-380,e_w31024391-380</t>
-  </si>
-  <si>
-    <t>e_w797009308-380,e_w1128250704-380,e_w883928229-380,e_w951773852-380,e_w32076853-380,e_w955268864-380</t>
-  </si>
-  <si>
-    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380,e_w24976300-380,e_DE183-380</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>e_w152018146-380,e_w88901626-380,e_w87653464-380,e_w87653464-400,e_w152261133-380,e_w31367940-380,e_w42049947-380,e_w26814283-380,e_DE217-380,e_DE202-380,e_w26404600-380,e_w26403575-380</t>
-  </si>
-  <si>
-    <t>e_w603661085-380,e_w946969736-380,e_w301158539-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE165-380,e_DE187-380,e_w1089568373-380,e_w944960289-380</t>
-  </si>
-  <si>
-    <t>e_DE152-380,e_w29713902-380,e_DE138-380,e_w714098678-380,e_DE161-380,e_DE160-380,e_w109917397-380,e_w942771541-380,e_w941805476-380</t>
-  </si>
-  <si>
-    <t>e_w30132758-380,e_w518455594-380,e_w1068350839-380,e_w940922557-380,e_w137197826-380,e_w30039908-380,e_w30164703-380,e_DE54-380,e_w414169327-380,e_w170123812-400</t>
-  </si>
-  <si>
-    <t>e_w156673636-380,e_DE121-380,e_w42681484-380,e_w148446247-380,e_w29309786-380,e_w948341123-380,e_w149256409-380,e_w143882655-380,e_w32690742-380</t>
-  </si>
-  <si>
-    <t>e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w24262656-380,e_DE51-380,e_w26474759-380</t>
-  </si>
-  <si>
-    <t>e_w59707532-380,e_w517421342-380,e_w851299584-380,e_DE14-380</t>
-  </si>
-  <si>
-    <t>e_w29472852-380,e_DE44-380,e_w24230738-380,e_DE41-380,e_w24413992-380,e_w27739871-380,e_w23899043-380</t>
-  </si>
-  <si>
-    <t>e_w143903369-380,e_w55069713-380,e_w42372159-380,e_w143854536-380,e_w31653753-380,e_w148446247-380,e_w38325076-380,e_w24705761-380,e_w24758329-380,e_w76246159-380,e_w28613721-380,e_w24757393-380,e_w24757392-380</t>
-  </si>
-  <si>
-    <t>e_w29713902-380,e_w943939310-380,e_w33169401-380,e_w946025110-380,e_DE34-380,e_w398680313-380,e_w28729619-380</t>
-  </si>
-  <si>
-    <t>e_DE63-380,e_DE48-380,e_w979801144-380,e_w61918154-380</t>
-  </si>
-  <si>
-    <t>e_w5404079-380,e_w26245195-380,e_w24976300-380</t>
-  </si>
-  <si>
-    <t>e_w31131325-380,e_w25306752-380,e_w31131320-380,e_w41389594-380,e_w57727004-380,e_w683227471-380,e_w88945213-380,e_DE240-380,e_w30613895-380,e_w53378027-380</t>
-  </si>
-  <si>
-    <t>e_w947118608-380,e_w941453716-380,e_w30039908-380,e_w1091984573-380,e_DE21-400,e_w943444232-380</t>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1102,10 +1144,22 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1132,16 +1186,16 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_007</t>
@@ -1174,58 +1228,46 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w683227471-380,e_w30613895-380</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w24976300-380</t>
   </si>
   <si>
     <t>elc_won_005</t>
@@ -1234,10 +1276,22 @@
     <t>e_w941453716-380,e_w1091984573-380,e_w943444232-380</t>
   </si>
   <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w42681484-380,e_w24413992-380,e_w952004951-380,e_w810315511-380,e_w953757606-380,e_DE52-380,e_w32690742-380,e_DE51-380</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w26245195-380,e_w24976300-380</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_DE165-380,e_DE152-380,e_w29713902-380,e_w944960289-380,e_DE138-380,e_w714098678-380,e_w946025110-380,e_DE160-380,e_w109917397-380</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1264,16 +1318,16 @@
     <t>e_w26404600-380,e_w26403575-380,e_w88945213-380,e_w38325076-380,e_w53378027-380,e_w76246159-380</t>
   </si>
   <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_DE188-380,e_w93341407-380,e_DE187-380,e_w1089568373-380,e_DE183-380,e_DE161-380</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w24976300-380</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_DE23-380,e_w797009308-380,e_w1280178911-380,e_w1128250704-380,e_w883928229-380,e_w31024391-380,e_w32076853-380,e_w603661085-380,e_w946969736-380</t>
   </si>
   <si>
     <t>elc_won_007</t>
@@ -1306,60 +1360,6 @@
     <t>e_w25306752-380,e_w41389594-380</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w30622610-380,e_w603661085-380,e_w301158539-380,e_w25306938-380,e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w275466323,e_w74893659-380,e_w234171369-380,e_DE8-380,e_w940919943</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w683227471-380,e_w30613895-380</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w943939310-380,e_w946025110-380,e_w398680313-380,e_w28729619-380,e_w942771541-380,e_w1068350839-380,e_w940922557-380,e_w941805476-380,e_w30164703-380,e_DE54-380</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w33169401-380,e_w59707532-380,e_w517421342-380,e_DE34-380,e_w851299584-380,e_DE14-380,e_w1094015892-380,e_w30132758-380,e_w518455594-380,e_w947118608-380,e_w941453716-380,e_w137197826-380,e_w30039908-380,e_w414169327-380,e_w170123812-400,e_DE21-400</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w26245195-380,e_w137602559-380,e_w77697810-380</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_DE165-380,e_DE152-380,e_w29713902-380,e_w944960289-380,e_DE138-380,e_w714098678-380,e_w946025110-380,e_DE160-380,e_w109917397-380</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_DE23-380,e_w797009308-380,e_w1280178911-380,e_w1128250704-380,e_w883928229-380,e_w31024391-380,e_w32076853-380,e_w603661085-380,e_w946969736-380</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_DE196-400,e_DE175-380,e_w152018146-380,e_w42097854-380,e_w152261133-380,e_w152107815-380,e_w198448981-380,e_w152973139-380,e_DE176-380</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w26245195-380,e_w24976300-380</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
@@ -1384,22 +1384,34 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wofelc_wof_007</t>
@@ -1408,18 +1420,6 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>elc_wof_003</t>
   </si>
   <si>
@@ -1444,37 +1444,37 @@
     <t>e_DE21-400</t>
   </si>
   <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w31024391-380,e_w946969736-380,e_w1134105414-380</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w275466323,e_w234171369-380</t>
+  </si>
+  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_DE8-380,e_w940919943</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w31024391-380,e_w946969736-380,e_w1134105414-380</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w275466323,e_w234171369-380</t>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
   </si>
   <si>
     <t>elc_wof_007</t>
   </si>
   <si>
     <t>e_w829116805-380,e_w289836713-380,e_DE16-380,e_DE13-380</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w35176751-380,e_w907539360-380,e_w1102237380-380,e_w74893659-380</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6618,7 +6618,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6C4863-F4A9-4E9A-B189-FA7B94A98094}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5744D520-1072-41CA-AFE7-7BE06E5E08D4}">
   <dimension ref="B9:BD33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6856,16 +6856,16 @@
         <v>249</v>
       </c>
       <c r="Y11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z11" t="s">
         <v>299</v>
       </c>
       <c r="AA11">
-        <v>0.99902896095987681</v>
+        <v>0.9984521235218653</v>
       </c>
       <c r="AB11">
-        <v>17.802382402257905</v>
+        <v>28.377735432469407</v>
       </c>
       <c r="AD11" t="s">
         <v>248</v>
@@ -6898,10 +6898,10 @@
         <v>367</v>
       </c>
       <c r="AO11">
-        <v>0.99753724381235709</v>
+        <v>0.99831023082457615</v>
       </c>
       <c r="AP11">
-        <v>45.150530106787691</v>
+        <v>30.979101549436738</v>
       </c>
       <c r="AR11" t="s">
         <v>248</v>
@@ -7002,16 +7002,16 @@
         <v>253</v>
       </c>
       <c r="Y12" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Z12" t="s">
         <v>300</v>
       </c>
       <c r="AA12">
-        <v>0.99815762041917688</v>
+        <v>0.99783818599396734</v>
       </c>
       <c r="AB12">
-        <v>33.776958981757815</v>
+        <v>39.633256777265125</v>
       </c>
       <c r="AD12" t="s">
         <v>248</v>
@@ -7044,10 +7044,10 @@
         <v>369</v>
       </c>
       <c r="AO12">
-        <v>0.99831023082457615</v>
+        <v>0.99810796133130941</v>
       </c>
       <c r="AP12">
-        <v>30.979101549436738</v>
+        <v>34.687375592660409</v>
       </c>
       <c r="AR12" t="s">
         <v>248</v>
@@ -7148,16 +7148,16 @@
         <v>255</v>
       </c>
       <c r="Y13" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="Z13" t="s">
         <v>301</v>
       </c>
       <c r="AA13">
-        <v>0.99786441593591435</v>
+        <v>0.9981906651950686</v>
       </c>
       <c r="AB13">
-        <v>39.152374508236058</v>
+        <v>33.171138090409563</v>
       </c>
       <c r="AD13" t="s">
         <v>248</v>
@@ -7190,10 +7190,10 @@
         <v>371</v>
       </c>
       <c r="AO13">
-        <v>0.99888649626708259</v>
+        <v>0.99798114961534334</v>
       </c>
       <c r="AP13">
-        <v>20.414235103486192</v>
+        <v>37.012257052039594</v>
       </c>
       <c r="AR13" t="s">
         <v>248</v>
@@ -7294,16 +7294,16 @@
         <v>257</v>
       </c>
       <c r="Y14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z14" t="s">
         <v>302</v>
       </c>
       <c r="AA14">
-        <v>0.99903141795748496</v>
+        <v>0.99837540256192037</v>
       </c>
       <c r="AB14">
-        <v>17.757337446108838</v>
+        <v>29.784286364794184</v>
       </c>
       <c r="AD14" t="s">
         <v>248</v>
@@ -7336,10 +7336,10 @@
         <v>373</v>
       </c>
       <c r="AO14">
-        <v>0.99888703680442148</v>
+        <v>0.99838078830661203</v>
       </c>
       <c r="AP14">
-        <v>20.404325252272194</v>
+        <v>29.68554771211182</v>
       </c>
       <c r="AR14" t="s">
         <v>248</v>
@@ -7440,16 +7440,16 @@
         <v>259</v>
       </c>
       <c r="Y15" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Z15" t="s">
         <v>303</v>
       </c>
       <c r="AA15">
-        <v>0.99797139203037322</v>
+        <v>0.99839933473711795</v>
       </c>
       <c r="AB15">
-        <v>37.191146109824579</v>
+        <v>29.345529819503312</v>
       </c>
       <c r="AD15" t="s">
         <v>248</v>
@@ -7482,10 +7482,10 @@
         <v>375</v>
       </c>
       <c r="AO15">
-        <v>0.99851437709898627</v>
+        <v>0.99852500850690518</v>
       </c>
       <c r="AP15">
-        <v>27.236419851917539</v>
+        <v>27.041510706738034</v>
       </c>
       <c r="AR15" t="s">
         <v>248</v>
@@ -7515,13 +7515,13 @@
         <v>438</v>
       </c>
       <c r="BB15" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="BC15">
-        <v>0.99726555940500838</v>
+        <v>0.98635566783526007</v>
       </c>
       <c r="BD15">
-        <v>50.131410908180094</v>
+        <v>250.14608968689959</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7586,16 +7586,16 @@
         <v>261</v>
       </c>
       <c r="Y16" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="Z16" t="s">
         <v>304</v>
       </c>
       <c r="AA16">
-        <v>0.99872758352859059</v>
+        <v>0.99887966592548594</v>
       </c>
       <c r="AB16">
-        <v>23.327635309172347</v>
+        <v>20.53945803275866</v>
       </c>
       <c r="AD16" t="s">
         <v>248</v>
@@ -7628,10 +7628,10 @@
         <v>377</v>
       </c>
       <c r="AO16">
-        <v>0.99835510064157384</v>
+        <v>0.99785502426144801</v>
       </c>
       <c r="AP16">
-        <v>30.156488237812564</v>
+        <v>39.324555206787501</v>
       </c>
       <c r="AR16" t="s">
         <v>248</v>
@@ -7658,10 +7658,10 @@
         <v>420</v>
       </c>
       <c r="BA16" t="s">
+        <v>439</v>
+      </c>
+      <c r="BB16" t="s">
         <v>440</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>441</v>
       </c>
       <c r="BC16">
         <v>0.99345136660650646</v>
@@ -7732,16 +7732,16 @@
         <v>263</v>
       </c>
       <c r="Y17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Z17" t="s">
         <v>305</v>
       </c>
       <c r="AA17">
-        <v>0.99783818599396734</v>
+        <v>0.99828989494874287</v>
       </c>
       <c r="AB17">
-        <v>39.633256777265125</v>
+        <v>31.351925939714036</v>
       </c>
       <c r="AD17" t="s">
         <v>248</v>
@@ -7774,10 +7774,10 @@
         <v>379</v>
       </c>
       <c r="AO17">
-        <v>0.99785502426144801</v>
+        <v>0.99667925950575054</v>
       </c>
       <c r="AP17">
-        <v>39.324555206787501</v>
+        <v>60.880242394574381</v>
       </c>
       <c r="AR17" t="s">
         <v>248</v>
@@ -7804,10 +7804,10 @@
         <v>422</v>
       </c>
       <c r="BA17" t="s">
+        <v>441</v>
+      </c>
+      <c r="BB17" t="s">
         <v>442</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>443</v>
       </c>
       <c r="BC17">
         <v>0.99861480954449533</v>
@@ -7878,16 +7878,16 @@
         <v>265</v>
       </c>
       <c r="Y18" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="Z18" t="s">
         <v>306</v>
       </c>
       <c r="AA18">
-        <v>0.99905448261210317</v>
+        <v>0.99831420288554851</v>
       </c>
       <c r="AB18">
-        <v>17.334485444775215</v>
+        <v>30.906280431611009</v>
       </c>
       <c r="AD18" t="s">
         <v>248</v>
@@ -7920,10 +7920,10 @@
         <v>381</v>
       </c>
       <c r="AO18">
-        <v>0.99667925950575054</v>
+        <v>0.99753724381235709</v>
       </c>
       <c r="AP18">
-        <v>60.880242394574381</v>
+        <v>45.150530106787691</v>
       </c>
       <c r="AR18" t="s">
         <v>248</v>
@@ -7950,16 +7950,16 @@
         <v>424</v>
       </c>
       <c r="BA18" t="s">
+        <v>443</v>
+      </c>
+      <c r="BB18" t="s">
         <v>444</v>
       </c>
-      <c r="BB18" t="s">
-        <v>445</v>
-      </c>
       <c r="BC18">
-        <v>0.99871075555058875</v>
+        <v>0.99726555940500838</v>
       </c>
       <c r="BD18">
-        <v>23.636148239206339</v>
+        <v>50.131410908180094</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8024,16 +8024,16 @@
         <v>267</v>
       </c>
       <c r="Y19" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s">
         <v>307</v>
       </c>
       <c r="AA19">
-        <v>0.99845115321674904</v>
+        <v>0.99786441593591435</v>
       </c>
       <c r="AB19">
-        <v>28.395524359600802</v>
+        <v>39.152374508236058</v>
       </c>
       <c r="AD19" t="s">
         <v>248</v>
@@ -8066,10 +8066,10 @@
         <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.9985540071847413</v>
+        <v>0.99664078053750105</v>
       </c>
       <c r="AP19">
-        <v>26.509868279743756</v>
+        <v>61.585690145814638</v>
       </c>
       <c r="AR19" t="s">
         <v>248</v>
@@ -8096,16 +8096,16 @@
         <v>426</v>
       </c>
       <c r="BA19" t="s">
+        <v>445</v>
+      </c>
+      <c r="BB19" t="s">
         <v>446</v>
       </c>
-      <c r="BB19" t="s">
-        <v>431</v>
-      </c>
       <c r="BC19">
-        <v>0.98635566783526007</v>
+        <v>0.99733561350881073</v>
       </c>
       <c r="BD19">
-        <v>250.14608968689959</v>
+        <v>48.847085671804372</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8170,16 +8170,16 @@
         <v>269</v>
       </c>
       <c r="Y20" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="Z20" t="s">
         <v>308</v>
       </c>
       <c r="AA20">
-        <v>0.99792185696155833</v>
+        <v>0.9966615805732193</v>
       </c>
       <c r="AB20">
-        <v>38.099289038098078</v>
+        <v>61.204356157646131</v>
       </c>
       <c r="AD20" t="s">
         <v>248</v>
@@ -8212,10 +8212,10 @@
         <v>385</v>
       </c>
       <c r="AO20">
-        <v>0.99912192348268269</v>
+        <v>0.99821483672858236</v>
       </c>
       <c r="AP20">
-        <v>16.098069484150571</v>
+        <v>32.727993309323963</v>
       </c>
       <c r="AR20" t="s">
         <v>248</v>
@@ -8248,10 +8248,10 @@
         <v>448</v>
       </c>
       <c r="BC20">
-        <v>0.99733561350881073</v>
+        <v>0.99871075555058875</v>
       </c>
       <c r="BD20">
-        <v>48.847085671804372</v>
+        <v>23.636148239206339</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8316,16 +8316,16 @@
         <v>271</v>
       </c>
       <c r="Y21" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="Z21" t="s">
         <v>309</v>
       </c>
       <c r="AA21">
-        <v>0.99783379528973448</v>
+        <v>0.99905448261210317</v>
       </c>
       <c r="AB21">
-        <v>39.713753021534231</v>
+        <v>17.334485444775215</v>
       </c>
       <c r="AD21" t="s">
         <v>248</v>
@@ -8358,10 +8358,10 @@
         <v>387</v>
       </c>
       <c r="AO21">
-        <v>0.99864092836530338</v>
+        <v>0.99851446571821256</v>
       </c>
       <c r="AP21">
-        <v>24.916313302771705</v>
+        <v>27.234795166103936</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8426,16 +8426,16 @@
         <v>273</v>
       </c>
       <c r="Y22" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s">
         <v>310</v>
       </c>
       <c r="AA22">
-        <v>0.99852845242200794</v>
+        <v>0.99845115321674904</v>
       </c>
       <c r="AB22">
-        <v>26.978372263188255</v>
+        <v>28.395524359600802</v>
       </c>
       <c r="AD22" t="s">
         <v>248</v>
@@ -8468,10 +8468,10 @@
         <v>389</v>
       </c>
       <c r="AO22">
-        <v>0.99840287720275267</v>
+        <v>0.99888649626708259</v>
       </c>
       <c r="AP22">
-        <v>29.280584616200382</v>
+        <v>20.414235103486192</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8536,16 +8536,16 @@
         <v>275</v>
       </c>
       <c r="Y23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s">
         <v>311</v>
       </c>
       <c r="AA23">
-        <v>0.99876909403276848</v>
+        <v>0.99792185696155833</v>
       </c>
       <c r="AB23">
-        <v>22.56660939924376</v>
+        <v>38.099289038098078</v>
       </c>
       <c r="AD23" t="s">
         <v>248</v>
@@ -8578,10 +8578,10 @@
         <v>391</v>
       </c>
       <c r="AO23">
-        <v>0.99798110605540413</v>
+        <v>0.99888703680442148</v>
       </c>
       <c r="AP23">
-        <v>37.013055650923285</v>
+        <v>20.404325252272194</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8646,16 +8646,16 @@
         <v>277</v>
       </c>
       <c r="Y24" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="Z24" t="s">
         <v>312</v>
       </c>
       <c r="AA24">
-        <v>0.9984521235218653</v>
+        <v>0.99783379528973448</v>
       </c>
       <c r="AB24">
-        <v>28.377735432469407</v>
+        <v>39.713753021534231</v>
       </c>
       <c r="AD24" t="s">
         <v>248</v>
@@ -8688,10 +8688,10 @@
         <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.99810796133130941</v>
+        <v>0.99851437709898627</v>
       </c>
       <c r="AP24">
-        <v>34.687375592660409</v>
+        <v>27.236419851917539</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8756,16 +8756,16 @@
         <v>279</v>
       </c>
       <c r="Y25" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="Z25" t="s">
         <v>313</v>
       </c>
       <c r="AA25">
-        <v>0.99837540256192037</v>
+        <v>0.99852845242200794</v>
       </c>
       <c r="AB25">
-        <v>29.784286364794184</v>
+        <v>26.978372263188255</v>
       </c>
       <c r="AD25" t="s">
         <v>248</v>
@@ -8798,10 +8798,10 @@
         <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.99798114961534334</v>
+        <v>0.99835510064157384</v>
       </c>
       <c r="AP25">
-        <v>37.012257052039594</v>
+        <v>30.156488237812564</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8866,16 +8866,16 @@
         <v>281</v>
       </c>
       <c r="Y26" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Z26" t="s">
         <v>314</v>
       </c>
       <c r="AA26">
-        <v>0.99839933473711795</v>
+        <v>0.99876909403276848</v>
       </c>
       <c r="AB26">
-        <v>29.345529819503312</v>
+        <v>22.56660939924376</v>
       </c>
       <c r="AD26" t="s">
         <v>248</v>
@@ -8908,10 +8908,10 @@
         <v>397</v>
       </c>
       <c r="AO26">
-        <v>0.99838078830661203</v>
+        <v>0.99853436339984547</v>
       </c>
       <c r="AP26">
-        <v>29.68554771211182</v>
+        <v>26.870004336166144</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8976,16 +8976,16 @@
         <v>283</v>
       </c>
       <c r="Y27" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="Z27" t="s">
         <v>315</v>
       </c>
       <c r="AA27">
-        <v>0.99887966592548594</v>
+        <v>0.9982564657516575</v>
       </c>
       <c r="AB27">
-        <v>20.53945803275866</v>
+        <v>31.964794552945094</v>
       </c>
       <c r="AD27" t="s">
         <v>248</v>
@@ -9018,10 +9018,10 @@
         <v>399</v>
       </c>
       <c r="AO27">
-        <v>0.99852500850690518</v>
+        <v>0.9982655473126083</v>
       </c>
       <c r="AP27">
-        <v>27.041510706738034</v>
+        <v>31.798299268848115</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9086,16 +9086,16 @@
         <v>285</v>
       </c>
       <c r="Y28" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Z28" t="s">
         <v>316</v>
       </c>
       <c r="AA28">
-        <v>0.99828989494874287</v>
+        <v>0.99854052945036897</v>
       </c>
       <c r="AB28">
-        <v>31.351925939714036</v>
+        <v>26.756960076568774</v>
       </c>
       <c r="AD28" t="s">
         <v>248</v>
@@ -9128,10 +9128,10 @@
         <v>401</v>
       </c>
       <c r="AO28">
-        <v>0.99821483672858236</v>
+        <v>0.9985540071847413</v>
       </c>
       <c r="AP28">
-        <v>32.727993309323963</v>
+        <v>26.509868279743756</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9196,16 +9196,16 @@
         <v>287</v>
       </c>
       <c r="Y29" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Z29" t="s">
         <v>317</v>
       </c>
       <c r="AA29">
-        <v>0.99831420288554851</v>
+        <v>0.99903141795748496</v>
       </c>
       <c r="AB29">
-        <v>30.906280431611009</v>
+        <v>17.757337446108838</v>
       </c>
       <c r="AD29" t="s">
         <v>248</v>
@@ -9238,10 +9238,10 @@
         <v>403</v>
       </c>
       <c r="AO29">
-        <v>0.99851446571821256</v>
+        <v>0.99912192348268269</v>
       </c>
       <c r="AP29">
-        <v>27.234795166103936</v>
+        <v>16.098069484150571</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9306,16 +9306,16 @@
         <v>289</v>
       </c>
       <c r="Y30" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Z30" t="s">
         <v>318</v>
       </c>
       <c r="AA30">
-        <v>0.9981906651950686</v>
+        <v>0.99797139203037322</v>
       </c>
       <c r="AB30">
-        <v>33.171138090409563</v>
+        <v>37.191146109824579</v>
       </c>
       <c r="AD30" t="s">
         <v>248</v>
@@ -9348,10 +9348,10 @@
         <v>405</v>
       </c>
       <c r="AO30">
-        <v>0.9982655473126083</v>
+        <v>0.99864092836530338</v>
       </c>
       <c r="AP30">
-        <v>31.798299268848115</v>
+        <v>24.916313302771705</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9416,16 +9416,16 @@
         <v>291</v>
       </c>
       <c r="Y31" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="Z31" t="s">
         <v>319</v>
       </c>
       <c r="AA31">
-        <v>0.9966615805732193</v>
+        <v>0.99872758352859059</v>
       </c>
       <c r="AB31">
-        <v>61.204356157646131</v>
+        <v>23.327635309172347</v>
       </c>
       <c r="AD31" t="s">
         <v>248</v>
@@ -9458,10 +9458,10 @@
         <v>407</v>
       </c>
       <c r="AO31">
-        <v>0.99853436339984547</v>
+        <v>0.99840287720275267</v>
       </c>
       <c r="AP31">
-        <v>26.870004336166144</v>
+        <v>29.280584616200382</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9526,16 +9526,16 @@
         <v>293</v>
       </c>
       <c r="Y32" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="Z32" t="s">
         <v>320</v>
       </c>
       <c r="AA32">
-        <v>0.9982564657516575</v>
+        <v>0.99902896095987681</v>
       </c>
       <c r="AB32">
-        <v>31.964794552945094</v>
+        <v>17.802382402257905</v>
       </c>
       <c r="AD32" t="s">
         <v>248</v>
@@ -9568,10 +9568,10 @@
         <v>409</v>
       </c>
       <c r="AO32">
-        <v>0.99664078053750105</v>
+        <v>0.99798110605540413</v>
       </c>
       <c r="AP32">
-        <v>61.585690145814638</v>
+        <v>37.013055650923285</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9636,16 +9636,16 @@
         <v>295</v>
       </c>
       <c r="Y33" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="Z33" t="s">
         <v>321</v>
       </c>
       <c r="AA33">
-        <v>0.99854052945036897</v>
+        <v>0.99815762041917688</v>
       </c>
       <c r="AB33">
-        <v>26.756960076568774</v>
+        <v>33.776958981757815</v>
       </c>
     </row>
   </sheetData>
@@ -9654,7 +9654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47938EE7-7B41-4EC3-86FA-4D177D8351F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0755BE93-AA26-416E-8B74-21F864414F69}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9766,7 +9766,7 @@
         <v>449</v>
       </c>
       <c r="K11" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="L11">
         <v>79.362778177778793</v>
@@ -9799,7 +9799,7 @@
         <v>493</v>
       </c>
       <c r="X11" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="Y11">
         <v>108.8275</v>
@@ -9834,7 +9834,7 @@
         <v>451</v>
       </c>
       <c r="K12" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="L12">
         <v>50.354564381123943</v>
@@ -9867,7 +9867,7 @@
         <v>495</v>
       </c>
       <c r="X12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y12">
         <v>54.292499999999997</v>
@@ -9902,7 +9902,7 @@
         <v>453</v>
       </c>
       <c r="K13" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="L13">
         <v>57.005439523831519</v>
@@ -9970,7 +9970,7 @@
         <v>455</v>
       </c>
       <c r="K14" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="L14">
         <v>19.895723562817633</v>
@@ -10038,7 +10038,7 @@
         <v>457</v>
       </c>
       <c r="K15" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L15">
         <v>9.5699994650614961</v>
@@ -10106,7 +10106,7 @@
         <v>459</v>
       </c>
       <c r="K16" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="L16">
         <v>44.760252416795389</v>
@@ -10174,7 +10174,7 @@
         <v>461</v>
       </c>
       <c r="K17" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="L17">
         <v>40.59880776523103</v>
@@ -10207,7 +10207,7 @@
         <v>505</v>
       </c>
       <c r="X17" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="Y17">
         <v>0.92625000000000002</v>
@@ -10242,7 +10242,7 @@
         <v>463</v>
       </c>
       <c r="K18" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="L18">
         <v>71.045385513132985</v>
@@ -10275,7 +10275,7 @@
         <v>507</v>
       </c>
       <c r="X18" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Y18">
         <v>7.5287499999999996</v>
@@ -10310,7 +10310,7 @@
         <v>465</v>
       </c>
       <c r="K19" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="L19">
         <v>63.055598832310729</v>
@@ -10343,7 +10343,7 @@
         <v>509</v>
       </c>
       <c r="X19" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Y19">
         <v>14.6</v>
@@ -10378,7 +10378,7 @@
         <v>467</v>
       </c>
       <c r="K20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="L20">
         <v>43.89469200396065</v>
@@ -10411,7 +10411,7 @@
         <v>511</v>
       </c>
       <c r="X20" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Y20">
         <v>0.24374999999999999</v>
@@ -10446,7 +10446,7 @@
         <v>469</v>
       </c>
       <c r="K21" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="L21">
         <v>11.547936358898198</v>
@@ -10481,7 +10481,7 @@
         <v>471</v>
       </c>
       <c r="K22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L22">
         <v>31.481356456094364</v>
@@ -10516,7 +10516,7 @@
         <v>473</v>
       </c>
       <c r="K23" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="L23">
         <v>15.708789779919334</v>
@@ -10551,7 +10551,7 @@
         <v>475</v>
       </c>
       <c r="K24" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L24">
         <v>20.814752751471318</v>
@@ -10586,7 +10586,7 @@
         <v>477</v>
       </c>
       <c r="K25" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="L25">
         <v>50.266717026070005</v>
@@ -10621,7 +10621,7 @@
         <v>479</v>
       </c>
       <c r="K26" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="L26">
         <v>56.728889145623882</v>
@@ -10656,7 +10656,7 @@
         <v>481</v>
       </c>
       <c r="K27" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="L27">
         <v>70.602917671125681</v>
@@ -10691,7 +10691,7 @@
         <v>483</v>
       </c>
       <c r="K28" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="L28">
         <v>7.8153674765988201</v>
@@ -10726,7 +10726,7 @@
         <v>485</v>
       </c>
       <c r="K29" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="L29">
         <v>26.861604762024118</v>
@@ -10761,7 +10761,7 @@
         <v>487</v>
       </c>
       <c r="K30" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="L30">
         <v>10.889866530825216</v>
@@ -10796,7 +10796,7 @@
         <v>489</v>
       </c>
       <c r="K31" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="L31">
         <v>9.0084683548455349</v>
@@ -10831,7 +10831,7 @@
         <v>491</v>
       </c>
       <c r="K32" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="L32">
         <v>35.009005865752776</v>
@@ -10846,7 +10846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD0DC41-4694-45E5-A8D3-D3202134CF60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D04916-8518-42C2-A95F-B64A0FB55073}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12663,7 +12663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D0CB45-5525-406B-862E-9FDA9DCD8B64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8DC279-9EFB-4949-9A91-1A88C0D5281D}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
